--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>4.15</v>
+        <v>3.82</v>
       </c>
       <c r="N22" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="N23" t="n">
-        <v>4.15</v>
+        <v>3.66</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,10 +3197,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA23" t="n">
         <v>2.5</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N24" t="n">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45981.22916666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>45981.66666666666</v>
+        <v>45981.625</v>
       </c>
     </row>
     <row r="21">
@@ -2879,27 +2879,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>45981.70833333334</v>
+        <v>45981.625</v>
       </c>
     </row>
     <row r="22">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>3.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>1.82</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.93</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>45981.75</v>
+        <v>45981.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>3.37</v>
       </c>
       <c r="M23" t="n">
-        <v>2.72</v>
+        <v>3.29</v>
       </c>
       <c r="N23" t="n">
-        <v>3.66</v>
+        <v>1.93</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>45981.8125</v>
+        <v>45981.70833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3236,116 +3236,354 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>45981.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3" t="n">
+        <v>45981.8125</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Ceará</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>2.06</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>2.93</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>3.39</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.5</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AB26" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3" t="n">
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3" t="n">
         <v>45981.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3060,7 +3060,7 @@
         <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="T22" t="n">
         <v>3.21</v>
@@ -3072,7 +3072,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
@@ -3167,40 +3167,40 @@
         <v>1.93</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA23" t="n">
         <v>1.81</v>
@@ -3209,22 +3209,22 @@
         <v>1.89</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45981.70833333334</v>
@@ -3286,40 +3286,40 @@
         <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA24" t="n">
         <v>1.77</v>
@@ -3328,22 +3328,22 @@
         <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45981.75</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.61</v>
@@ -686,7 +686,7 @@
         <v>3.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
         <v>7.5</v>
@@ -725,7 +725,7 @@
         <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45981.22916666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3405,34 +3405,34 @@
         <v>3.66</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
         <v>1.47</v>
@@ -3447,22 +3447,22 @@
         <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45981.8125</v>
@@ -3524,40 +3524,40 @@
         <v>3.39</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA26" t="n">
         <v>2.5</v>
@@ -3566,22 +3566,22 @@
         <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45981.89583333334</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,14 +2801,14 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N20" t="n">
         <v>2.6</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3051,13 +3051,13 @@
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
         <v>2.79</v>
@@ -3066,7 +3066,7 @@
         <v>3.21</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
         <v>8.300000000000001</v>
@@ -3075,13 +3075,13 @@
         <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="AA22" t="n">
         <v>2.05</v>
@@ -3096,16 +3096,16 @@
         <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AF22" t="n">
         <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.93</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.66666666666</v>
@@ -3167,13 +3167,13 @@
         <v>1.93</v>
       </c>
       <c r="O23" t="n">
-        <v>3.79</v>
+        <v>3.45</v>
       </c>
       <c r="P23" t="n">
         <v>2.11</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
         <v>1.36</v>
@@ -3185,19 +3185,19 @@
         <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
         <v>3.44</v>
@@ -3218,13 +3218,13 @@
         <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
         <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45981.70833333334</v>
@@ -3286,22 +3286,22 @@
         <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="P24" t="n">
         <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.75</v>
+        <v>5.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
         <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="U24" t="n">
         <v>1.44</v>
@@ -3316,10 +3316,10 @@
         <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AA24" t="n">
         <v>1.77</v>
@@ -3334,7 +3334,7 @@
         <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
         <v>1.9</v>
@@ -3343,7 +3343,7 @@
         <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45981.75</v>
@@ -3405,31 +3405,31 @@
         <v>3.66</v>
       </c>
       <c r="O25" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
         <v>1.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="R25" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
         <v>1.07</v>
@@ -3447,10 +3447,10 @@
         <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.89</v>
+        <v>4.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE25" t="n">
         <v>2.06</v>
@@ -3545,16 +3545,16 @@
         <v>1.27</v>
       </c>
       <c r="V26" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z26" t="n">
         <v>2.48</v>
@@ -3572,10 +3572,10 @@
         <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
         <v>1.36</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -665,31 +665,31 @@
         <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="P2" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="U2" t="n">
         <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -701,19 +701,19 @@
         <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
         <v>1.79</v>
@@ -722,10 +722,10 @@
         <v>1.88</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45981.22916666666</v>
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6.2</v>
+        <v>5.93</v>
       </c>
       <c r="O4" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.84</v>
+        <v>5.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
         <v>6.6</v>
@@ -933,7 +933,7 @@
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
         <v>1.21</v>
@@ -942,28 +942,28 @@
         <v>3.58</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.81</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,14 +2920,14 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N21" t="n">
         <v>2.6</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.37</v>
+        <v>2.93</v>
       </c>
       <c r="M23" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="O23" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45981.70833333334</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,14 +2801,14 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N20" t="n">
         <v>2.6</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3039,31 +3039,31 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
         <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
         <v>1.32</v>
@@ -3072,37 +3072,37 @@
         <v>8.300000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.06</v>
+        <v>3.88</v>
       </c>
       <c r="AD22" t="n">
         <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="n">
         <v>1.23</v>
@@ -3286,46 +3286,46 @@
         <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="P24" t="n">
         <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="R24" t="n">
         <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
         <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
         <v>3.62</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
         <v>2.85</v>
@@ -3334,16 +3334,16 @@
         <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
         <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45981.75</v>
@@ -3396,31 +3396,31 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.66</v>
+        <v>4.01</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P25" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
         <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U25" t="n">
         <v>1.26</v>
@@ -3432,34 +3432,34 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.4</v>
+        <v>4.89</v>
       </c>
       <c r="AD25" t="n">
         <v>1.14</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
         <v>1.67</v>
@@ -3515,25 +3515,25 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
         <v>2.88</v>
       </c>
       <c r="P26" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
         <v>2.39</v>
@@ -3545,40 +3545,40 @@
         <v>1.27</v>
       </c>
       <c r="V26" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.05</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="AA26" t="n">
         <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
         <v>4.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
         <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
         <v>1.66</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="M2" t="n">
         <v>3.25</v>
@@ -668,13 +668,13 @@
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -683,10 +683,10 @@
         <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>7.8</v>
@@ -695,13 +695,13 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.98</v>
@@ -710,22 +710,22 @@
         <v>1.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45981.22916666666</v>
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
         <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="P4" t="n">
         <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.94</v>
+        <v>6.11</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
         <v>2.88</v>
@@ -924,7 +924,7 @@
         <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
         <v>6.6</v>
@@ -945,25 +945,25 @@
         <v>1.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
         <v>1.81</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -1094,27 +1094,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>45981.42708333334</v>
+        <v>45981.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45981.45833333334</v>
+        <v>45981.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45981.5</v>
+        <v>45981.42708333334</v>
       </c>
     </row>
     <row r="9">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>45981.52083333334</v>
+        <v>45981.5</v>
       </c>
     </row>
     <row r="17">
@@ -2403,27 +2403,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JDFS Alberts</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>45981.54166666666</v>
+        <v>45981.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JDFS Alberts</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2641,27 +2641,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,37 +2721,37 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>45981.54166666666</v>
+        <v>45981.625</v>
       </c>
     </row>
     <row r="20">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2929,13 +2929,13 @@
         <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2944,25 +2944,25 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA21" t="n">
         <v>1.72</v>
@@ -2971,22 +2971,22 @@
         <v>1.98</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -2998,27 +2998,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>45981.66666666666</v>
+        <v>45981.625</v>
       </c>
     </row>
     <row r="23">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.93</v>
+        <v>3.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.08</v>
+        <v>2.79</v>
       </c>
       <c r="T23" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>45981.70833333334</v>
+        <v>45981.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3236,27 +3236,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>3.37</v>
       </c>
       <c r="M24" t="n">
-        <v>3.82</v>
+        <v>3.29</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>1.93</v>
       </c>
       <c r="O24" t="n">
-        <v>2.07</v>
+        <v>3.86</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.7</v>
+        <v>2.76</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="T24" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
         <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>45981.75</v>
+        <v>45981.70833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.82</v>
       </c>
       <c r="N25" t="n">
-        <v>4.01</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>2.31</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>3.3</v>
+        <v>2.57</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.66</v>
+        <v>3.62</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.89</v>
+        <v>2.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.67</v>
+        <v>2.29</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>45981.8125</v>
+        <v>45981.75</v>
       </c>
     </row>
     <row r="26">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,75 +3515,194 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="M26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="O26" t="n">
         <v>2.9</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.88</v>
-      </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R26" t="n">
         <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AA26" t="n">
         <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF26" t="n">
         <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" s="3" t="n">
+        <v>45981.8125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V27" t="n">
+        <v>10</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI27" s="3" t="n">
         <v>45981.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="M2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N2" t="n">
         <v>3.25</v>
       </c>
-      <c r="N2" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O2" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
         <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
         <v>7.8</v>
@@ -698,16 +698,16 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC2" t="n">
         <v>3.5</v>
@@ -716,16 +716,16 @@
         <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45981.22916666666</v>
@@ -909,7 +909,7 @@
         <v>2.03</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
         <v>6.11</v>
@@ -921,13 +921,13 @@
         <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="U4" t="n">
         <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
@@ -945,25 +945,25 @@
         <v>1.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AC4" t="n">
         <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45981.52083333334</v>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.17</v>
+        <v>2.94</v>
       </c>
       <c r="T24" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
         <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45981.70833333334</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2444,61 +2444,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V17" t="n">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="n">
         <v>1.75</v>
@@ -2572,64 +2572,64 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45981.54166666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,34 +2721,34 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45981.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2944,49 +2944,49 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O23" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="R23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.4</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="V23" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.88</v>
+        <v>3.54</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45981.66666666666</v>
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="M25" t="n">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="O25" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.57</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AD25" t="n">
         <v>1.48</v>
       </c>
-      <c r="V25" t="n">
-        <v>6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45981.75</v>
@@ -3515,22 +3515,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="N26" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
         <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="R26" t="n">
         <v>1.5</v>
@@ -3542,46 +3542,46 @@
         <v>3.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45981.8125</v>
@@ -3634,16 +3634,16 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="N27" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
         <v>1.92</v>
@@ -3652,7 +3652,7 @@
         <v>4.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
         <v>2.39</v>
@@ -3661,16 +3661,16 @@
         <v>3.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
         <v>1.43</v>
@@ -3682,7 +3682,7 @@
         <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC27" t="n">
         <v>4.75</v>
@@ -3691,16 +3691,16 @@
         <v>1.13</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45981.89583333334</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1192,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2453,34 +2453,34 @@
         <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>6.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="T17" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="U17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V17" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.22</v>
@@ -2501,10 +2501,10 @@
         <v>1.57</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
         <v>1.2</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T20" t="n">
         <v>2.56</v>
@@ -2831,13 +2831,13 @@
         <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
         <v>1.21</v>
@@ -2846,28 +2846,28 @@
         <v>3.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,28 +3039,28 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N22" t="n">
         <v>2.6</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.2</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.04</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
         <v>2.56</v>
@@ -3069,7 +3069,7 @@
         <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="W22" t="n">
         <v>1.07</v>
@@ -3084,28 +3084,28 @@
         <v>3.58</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>
@@ -3158,19 +3158,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O23" t="n">
         <v>4.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
         <v>2.35</v>
@@ -3182,7 +3182,7 @@
         <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
         <v>1.4</v>
@@ -3197,22 +3197,22 @@
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
         <v>3.12</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
         <v>3.54</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
         <v>1.96</v>
@@ -3277,34 +3277,34 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="O24" t="n">
         <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
         <v>7</v>
@@ -3313,34 +3313,34 @@
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC24" t="n">
         <v>2.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
         <v>1.33</v>
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="N25" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="P25" t="n">
         <v>2.56</v>
@@ -3426,7 +3426,7 @@
         <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="W25" t="n">
         <v>1.09</v>
@@ -3438,19 +3438,19 @@
         <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
         <v>2.57</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE25" t="n">
         <v>1.73</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.37</v>
+        <v>2.09</v>
       </c>
       <c r="M26" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="O26" t="n">
         <v>2.9</v>
@@ -3533,52 +3533,52 @@
         <v>3.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26" t="n">
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>5.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF26" t="n">
         <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
         <v>1.57</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="M27" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="O27" t="n">
         <v>2.88</v>
@@ -3661,46 +3661,46 @@
         <v>3.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y27" t="n">
         <v>1.43</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AA27" t="n">
         <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
         <v>4.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45981.89583333334</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>2.6</v>
@@ -677,16 +677,16 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>7.8</v>
@@ -695,22 +695,22 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
         <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD2" t="n">
         <v>1.22</v>
@@ -722,10 +722,10 @@
         <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45981.22916666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1192,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1311,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M20" t="n">
         <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.2</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.04</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
         <v>2.56</v>
@@ -2831,13 +2831,13 @@
         <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
         <v>1.21</v>
@@ -2852,22 +2852,22 @@
         <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,28 +3039,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
         <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T22" t="n">
         <v>2.56</v>
@@ -3069,13 +3069,13 @@
         <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
         <v>1.21</v>
@@ -3090,22 +3090,22 @@
         <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.66</v>
+        <v>3.74</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>6.55</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.79</v>
+        <v>2.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
         <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1263,34 +1263,34 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
@@ -1305,22 +1305,22 @@
         <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AF7" t="n">
         <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="M8" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
         <v>2.5</v>
@@ -1430,16 +1430,16 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45981.42708333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2453,40 +2453,40 @@
         <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>6.28</v>
+        <v>5.94</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA17" t="n">
         <v>1.53</v>
@@ -2501,13 +2501,13 @@
         <v>1.57</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
         <v>1.11</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>2.19</v>
       </c>
       <c r="M19" t="n">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="N19" t="n">
-        <v>6.2</v>
+        <v>2.54</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2721,28 +2721,28 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AF19" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.45</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.5</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V20" t="n">
+        <v>11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.33</v>
       </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3167,40 +3167,40 @@
         <v>1.82</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V23" t="n">
         <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
         <v>1.95</v>
@@ -3209,19 +3209,19 @@
         <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AF23" t="n">
         <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
         <v>1.22</v>
@@ -3286,7 +3286,7 @@
         <v>1.93</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
         <v>2.2</v>
@@ -3295,7 +3295,7 @@
         <v>2.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3304,13 +3304,13 @@
         <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -3319,7 +3319,7 @@
         <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.6</v>
+        <v>4.06</v>
       </c>
       <c r="AA24" t="n">
         <v>1.81</v>
@@ -3334,13 +3334,13 @@
         <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
         <v>1.33</v>
@@ -3405,10 +3405,10 @@
         <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
         <v>5.1</v>
@@ -3420,25 +3420,25 @@
         <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="U25" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>5.45</v>
+        <v>5.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA25" t="n">
         <v>1.77</v>
@@ -3447,22 +3447,22 @@
         <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE25" t="n">
         <v>1.73</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
         <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45981.75</v>
@@ -3524,34 +3524,34 @@
         <v>3.66</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="T26" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U26" t="n">
         <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
         <v>1.47</v>
@@ -3566,13 +3566,13 @@
         <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AF26" t="n">
         <v>1.73</v>
@@ -3643,40 +3643,40 @@
         <v>3.39</v>
       </c>
       <c r="O27" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
         <v>1.43</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AA27" t="n">
         <v>2.5</v>
@@ -3685,7 +3685,7 @@
         <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD27" t="n">
         <v>1.17</v>
@@ -3694,10 +3694,10 @@
         <v>2.13</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
         <v>1.65</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -680,13 +680,13 @@
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
         <v>7.8</v>
@@ -695,13 +695,13 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA2" t="n">
         <v>1.98</v>
@@ -713,19 +713,19 @@
         <v>3.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
         <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45981.22916666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>3.93</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V4" t="n">
-        <v>6.55</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.79</v>
+        <v>2.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>5.45</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.92</v>
+        <v>1.98</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.45</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>3.74</v>
+        <v>2.66</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>6.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.62</v>
+        <v>1.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
         <v>3.75</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O7" t="n">
         <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="AD7" t="n">
         <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2444,70 +2444,70 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
-        <v>5.94</v>
+        <v>5.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
         <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.16</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="n">
         <v>1.11</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45981.625</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.26</v>
+        <v>3.62</v>
       </c>
       <c r="N20" t="n">
-        <v>6.2</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AF20" t="n">
         <v>2.5</v>
       </c>
-      <c r="AA20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T21" t="n">
         <v>3.5</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.33</v>
       </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.49</v>
+        <v>2.02</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3158,34 +3158,34 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="O23" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
         <v>2.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
         <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
         <v>8</v>
@@ -3197,34 +3197,34 @@
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AF23" t="n">
         <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45981.66666666666</v>
@@ -3396,37 +3396,37 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>6.03</v>
       </c>
       <c r="O25" t="n">
         <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="R25" t="n">
         <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U25" t="n">
         <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="W25" t="n">
         <v>1.12</v>
@@ -3438,13 +3438,13 @@
         <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
         <v>2.51</v>
@@ -3462,7 +3462,7 @@
         <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45981.75</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="N26" t="n">
-        <v>3.66</v>
+        <v>3.15</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
         <v>1.44</v>
@@ -3554,19 +3554,19 @@
         <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AD26" t="n">
         <v>1.14</v>
@@ -3581,7 +3581,7 @@
         <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45981.8125</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="M27" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="N27" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>2.85</v>
@@ -3652,10 +3652,10 @@
         <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="T27" t="n">
         <v>3.3</v>
@@ -3667,40 +3667,40 @@
         <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y27" t="n">
         <v>1.43</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AA27" t="n">
         <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC27" t="n">
         <v>4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45981.89583333334</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45981.33333333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.03</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>6.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
         <v>1.55</v>
@@ -1180,28 +1180,28 @@
         <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>3.03</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1382,64 +1382,64 @@
         <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
         <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.82</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.81</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45981.42708333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2563,34 +2563,34 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="P18" t="n">
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.11</v>
+        <v>4.64</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
         <v>6</v>
@@ -2608,10 +2608,10 @@
         <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
         <v>2.75</v>
@@ -2620,16 +2620,16 @@
         <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45981.54166666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,40 +2682,40 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
         <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="T19" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
@@ -2727,28 +2727,28 @@
         <v>3.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45981.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="P20" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC20" t="n">
         <v>3</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -2920,28 +2920,28 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="M21" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="N21" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O21" t="n">
         <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.4</v>
+        <v>6.93</v>
       </c>
       <c r="R21" t="n">
         <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="T21" t="n">
         <v>3.5</v>
@@ -2950,7 +2950,7 @@
         <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="W21" t="n">
         <v>1.03</v>
@@ -2959,22 +2959,22 @@
         <v>1.07</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.4</v>
       </c>
-      <c r="AA21" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
         <v>4.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE21" t="n">
         <v>2.38</v>
@@ -2986,7 +2986,7 @@
         <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3042,70 +3042,70 @@
         <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="N22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2.5</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>
@@ -3277,31 +3277,31 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O24" t="n">
         <v>3.37</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.55</v>
-      </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
         <v>1.46</v>
@@ -3310,7 +3310,7 @@
         <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -3319,13 +3319,13 @@
         <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
         <v>2.83</v>
@@ -3337,7 +3337,7 @@
         <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG24" t="n">
         <v>1.25</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.93</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>6.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>3.93</v>
       </c>
       <c r="O5" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>6.55</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.79</v>
+        <v>2.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>5.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.1</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>1.55</v>
@@ -1180,28 +1180,28 @@
         <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,43 +1254,43 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.03</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>6.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
@@ -1299,28 +1299,28 @@
         <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2444,28 +2444,28 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
         <v>5.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
         <v>2.33</v>
@@ -2477,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
@@ -2486,25 +2486,25 @@
         <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG17" t="n">
         <v>2.63</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T19" t="n">
         <v>3.5</v>
       </c>
-      <c r="N19" t="n">
+      <c r="U19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V19" t="n">
+        <v>11</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.5</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="AA19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.33</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45981.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
         <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
         <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.59</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.93</v>
+        <v>3.38</v>
       </c>
       <c r="R21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.57</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V21" t="n">
-        <v>11</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="M23" t="n">
         <v>3.6</v>
@@ -3182,7 +3182,7 @@
         <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
         <v>1.36</v>
@@ -3200,10 +3200,10 @@
         <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB23" t="n">
         <v>1.8</v>
@@ -3212,19 +3212,19 @@
         <v>3.44</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
         <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45981.66666666666</v>
@@ -3396,52 +3396,52 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>6.03</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="P25" t="n">
         <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
         <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="U25" t="n">
         <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>2.25</v>
@@ -3450,19 +3450,19 @@
         <v>2.51</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
         <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45981.75</v>
@@ -3515,34 +3515,34 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="N26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="T26" t="n">
         <v>3.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
         <v>10</v>
@@ -3551,22 +3551,22 @@
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AD26" t="n">
         <v>1.14</v>
@@ -3578,10 +3578,10 @@
         <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45981.8125</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
         <v>2.87</v>
@@ -3643,64 +3643,64 @@
         <v>3.25</v>
       </c>
       <c r="O27" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="T27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
         <v>1.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AA27" t="n">
         <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AC27" t="n">
         <v>4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45981.89583333334</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
         <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -698,16 +698,16 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
         <v>3.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
         <v>3.7</v>
@@ -722,10 +722,10 @@
         <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45981.22916666666</v>
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="T3" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="U3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
         <v>6.5</v>
@@ -823,28 +823,28 @@
         <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45981.33333333334</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>4.3</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>7.37</v>
       </c>
       <c r="O4" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="P4" t="n">
         <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -921,49 +921,49 @@
         <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
         <v>6.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
         <v>1.79</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC4" t="n">
         <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
         <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.03</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>2.62</v>
+        <v>3.36</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>4.84</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
         <v>1.55</v>
@@ -1180,28 +1180,28 @@
         <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,43 +1254,43 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.1</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
@@ -1299,28 +1299,28 @@
         <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>2.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.06</v>
+        <v>4.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="U8" t="n">
         <v>1.39</v>
@@ -1412,34 +1412,34 @@
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.27</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45981.42708333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2453,19 +2453,19 @@
         <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>5.95</v>
+        <v>4.46</v>
       </c>
       <c r="P17" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="T17" t="n">
         <v>2.33</v>
@@ -2486,7 +2486,7 @@
         <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
         <v>1.53</v>
@@ -2507,7 +2507,7 @@
         <v>1.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.63</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
         <v>1.11</v>
@@ -2572,34 +2572,34 @@
         <v>2.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="U18" t="n">
         <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
         <v>1.2</v>
@@ -2611,25 +2611,25 @@
         <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
         <v>1.65</v>
       </c>
       <c r="AF18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH18" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45981.54166666666</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>2.19</v>
       </c>
       <c r="M19" t="n">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="N19" t="n">
-        <v>6.2</v>
+        <v>2.54</v>
       </c>
       <c r="O19" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.3</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V19" t="n">
-        <v>11</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AC19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AF19" t="n">
         <v>2.5</v>
       </c>
-      <c r="AA19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45981.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,70 +2801,70 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.29</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AH20" t="n">
         <v>1.44</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="O21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T21" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="U21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
         <v>1.07</v>
@@ -2959,34 +2959,34 @@
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
         <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>1.59</v>
       </c>
       <c r="M22" t="n">
-        <v>3.62</v>
+        <v>3.26</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>6.2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.87</v>
+        <v>2.28</v>
       </c>
       <c r="P22" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>5.22</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.53</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.37</v>
+        <v>3.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="O23" t="n">
         <v>4.5</v>
@@ -3176,22 +3176,22 @@
         <v>2.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -3203,19 +3203,19 @@
         <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
         <v>1.85</v>
@@ -3224,7 +3224,7 @@
         <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45981.66666666666</v>
@@ -3277,34 +3277,34 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="M24" t="n">
-        <v>3.42</v>
+        <v>3.29</v>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="O24" t="n">
-        <v>3.37</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
         <v>6.5</v>
@@ -3313,34 +3313,34 @@
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
         <v>1.33</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>3.82</v>
       </c>
       <c r="N25" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
         <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="R25" t="n">
         <v>1.27</v>
@@ -3420,13 +3420,13 @@
         <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="U25" t="n">
         <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="W25" t="n">
         <v>1.09</v>
@@ -3435,34 +3435,34 @@
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE25" t="n">
         <v>1.79</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AG25" t="n">
         <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45981.75</v>
@@ -3515,61 +3515,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="M26" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="Q26" t="n">
         <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S26" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U26" t="n">
         <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W26" t="n">
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" t="n">
         <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE26" t="n">
         <v>2.05</v>
@@ -3634,16 +3634,16 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="M27" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
@@ -3673,16 +3673,16 @@
         <v>1.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AA27" t="n">
         <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
         <v>4.8</v>
@@ -3694,7 +3694,7 @@
         <v>2.19</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
         <v>1.33</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
         <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R3" t="n">
         <v>1.38</v>
@@ -823,10 +823,10 @@
         <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC3" t="n">
         <v>2.97</v>
@@ -835,16 +835,16 @@
         <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45981.33333333334</v>
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>7.37</v>
+        <v>6.56</v>
       </c>
       <c r="O4" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
         <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="V4" t="n">
         <v>6.55</v>
@@ -933,13 +933,13 @@
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="AA4" t="n">
         <v>1.79</v>
@@ -951,19 +951,19 @@
         <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
         <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>3.36</v>
+        <v>3.19</v>
       </c>
       <c r="N6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="O6" t="n">
         <v>2.38</v>
@@ -1150,10 +1150,10 @@
         <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.84</v>
+        <v>5.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
         <v>2.3</v>
@@ -1162,13 +1162,13 @@
         <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1.11</v>
@@ -1177,13 +1177,13 @@
         <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
         <v>4.95</v>
@@ -1192,13 +1192,13 @@
         <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH6" t="n">
         <v>1.89</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>2.24</v>
@@ -1388,16 +1388,16 @@
         <v>2.21</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.9</v>
+        <v>4.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="U8" t="n">
         <v>1.39</v>
@@ -1418,10 +1418,10 @@
         <v>3.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
         <v>2.97</v>
@@ -1430,16 +1430,16 @@
         <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45981.42708333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.19</v>
+        <v>2.54</v>
       </c>
       <c r="M19" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
         <v>2.54</v>
       </c>
       <c r="O19" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45981.625</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="M20" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.08</v>
+        <v>5.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>5.22</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>2.24</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.45</v>
       </c>
-      <c r="V20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.59</v>
+        <v>2.4</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.26</v>
+        <v>1.48</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.54</v>
+        <v>2.07</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>2.54</v>
+        <v>3.08</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W21" t="n">
         <v>1.07</v>
@@ -2962,7 +2962,7 @@
         <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.75</v>
@@ -2971,19 +2971,19 @@
         <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AH21" t="n">
         <v>1.44</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.59</v>
+        <v>2.19</v>
       </c>
       <c r="M22" t="n">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="N22" t="n">
-        <v>6.2</v>
+        <v>2.54</v>
       </c>
       <c r="O22" t="n">
-        <v>2.28</v>
+        <v>2.87</v>
       </c>
       <c r="P22" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.22</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.55</v>
       </c>
-      <c r="S22" t="n">
+      <c r="AB22" t="n">
         <v>2.3</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V22" t="n">
-        <v>11</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AC22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AF22" t="n">
         <v>2.5</v>
       </c>
-      <c r="AA22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>6.56</v>
+        <v>4.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>5.99</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>6.55</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.86</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.79</v>
+        <v>2.46</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>6.56</v>
       </c>
       <c r="O5" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="V5" t="n">
-        <v>8.6</v>
+        <v>6.55</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>3.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.62</v>
+        <v>1.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.43</v>
+        <v>2.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>5.9</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
         <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2453,13 +2453,13 @@
         <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>4.46</v>
+        <v>5.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -2486,7 +2486,7 @@
         <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA17" t="n">
         <v>1.53</v>
@@ -2501,13 +2501,13 @@
         <v>1.57</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
         <v>1.11</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.54</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="N19" t="n">
-        <v>2.54</v>
+        <v>3.08</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
         <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
         <v>1.75</v>
@@ -2733,19 +2733,19 @@
         <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
         <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AH19" t="n">
         <v>1.44</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.61</v>
+        <v>2.54</v>
       </c>
       <c r="M20" t="n">
         <v>3.2</v>
       </c>
       <c r="N20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V20" t="n">
         <v>5.5</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>3.72</v>
       </c>
       <c r="N21" t="n">
-        <v>3.08</v>
+        <v>2.54</v>
       </c>
       <c r="O21" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="P21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC21" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.19</v>
+        <v>1.59</v>
       </c>
       <c r="M22" t="n">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="N22" t="n">
-        <v>2.54</v>
+        <v>6.2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>5.22</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>4.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>
@@ -3167,37 +3167,37 @@
         <v>1.82</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="P23" t="n">
         <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R23" t="n">
         <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
         <v>3.25</v>
@@ -3209,7 +3209,7 @@
         <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AD23" t="n">
         <v>1.25</v>
@@ -3221,7 +3221,7 @@
         <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
         <v>1.22</v>
@@ -3286,31 +3286,31 @@
         <v>1.93</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
         <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
         <v>1.04</v>
@@ -3319,7 +3319,7 @@
         <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="AA24" t="n">
         <v>1.81</v>
@@ -3331,16 +3331,16 @@
         <v>2.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
         <v>1.33</v>
@@ -3411,22 +3411,22 @@
         <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
         <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
         <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.09</v>
@@ -3435,10 +3435,10 @@
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA25" t="n">
         <v>1.77</v>
@@ -3447,16 +3447,16 @@
         <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
         <v>1.2</v>
@@ -3524,19 +3524,19 @@
         <v>3.66</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P26" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
         <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="S26" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="T26" t="n">
         <v>3.42</v>
@@ -3548,10 +3548,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y26" t="n">
         <v>1.5</v>
@@ -3566,7 +3566,7 @@
         <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AD26" t="n">
         <v>1.17</v>
@@ -3575,7 +3575,7 @@
         <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG26" t="n">
         <v>1.4</v>
@@ -3643,37 +3643,37 @@
         <v>3.39</v>
       </c>
       <c r="O27" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R27" t="n">
         <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
         <v>1.27</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
         <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z27" t="n">
         <v>2.5</v>
@@ -3685,19 +3685,19 @@
         <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.8</v>
+        <v>5.11</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
         <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
         <v>1.65</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3.19</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>5.9</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
         <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AB6" t="n">
         <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,19 +1228,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>5.9</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AB7" t="n">
         <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1356,20 +1356,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="M19" t="n">
-        <v>3.41</v>
+        <v>3.72</v>
       </c>
       <c r="N19" t="n">
-        <v>3.08</v>
+        <v>2.54</v>
       </c>
       <c r="O19" t="n">
-        <v>3.03</v>
+        <v>2.87</v>
       </c>
       <c r="P19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45981.625</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.19</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.54</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>2.59</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.59</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V22" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.48</v>
+        <v>2.26</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2440,26 +2440,26 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>6.69</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="O17" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -2468,49 +2468,49 @@
         <v>3.11</v>
       </c>
       <c r="T17" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AF17" t="n">
         <v>2.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45981.52083333334</v>
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>6.05</v>
+        <v>5.55</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45981.54166666666</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.19</v>
+        <v>3.01</v>
       </c>
       <c r="M19" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>2.87</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
         <v>2.2</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,49 +2801,49 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.54</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="N20" t="n">
-        <v>2.54</v>
+        <v>3.08</v>
       </c>
       <c r="O20" t="n">
-        <v>3.22</v>
+        <v>3.03</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA20" t="n">
         <v>1.75</v>
@@ -2852,19 +2852,19 @@
         <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
         <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AH20" t="n">
         <v>1.44</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.63</v>
+        <v>2.54</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
         <v>5.5</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>9</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.36</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.94</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.08</v>
+        <v>5.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.03</v>
+        <v>2.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.95</v>
+        <v>5.25</v>
       </c>
       <c r="R22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.3</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,25 +871,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.9</v>
+        <v>6.56</v>
       </c>
       <c r="O4" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.99</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>6.55</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>3.86</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.46</v>
+        <v>1.79</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.48</v>
+        <v>2.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>6.56</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="P5" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>5.99</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>6.55</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.86</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.79</v>
+        <v>2.46</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>5.9</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
         <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,23 +1228,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>3.19</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>5.9</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AB7" t="n">
         <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,99 +2656,99 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.01</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.08</v>
       </c>
       <c r="O19" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45981.625</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="M20" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.08</v>
+        <v>5.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.03</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>5.25</v>
       </c>
       <c r="R20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.3</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,99 +2894,99 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.54</v>
+        <v>3.01</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45981.625</v>
@@ -3003,109 +3003,109 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.63</v>
+        <v>2.54</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
         <v>5.5</v>
       </c>
-      <c r="O22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V22" t="n">
-        <v>9</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>
@@ -3141,90 +3141,90 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="O23" t="n">
-        <v>4.85</v>
+        <v>4.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="T23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.9</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V23" t="n">
-        <v>8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AA23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45981.66666666666</v>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.37</v>
+        <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
         <v>3.62</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45981.70833333334</v>
@@ -3396,37 +3396,37 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.56</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.52</v>
-      </c>
       <c r="V25" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W25" t="n">
         <v>1.09</v>
@@ -3438,31 +3438,31 @@
         <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD25" t="n">
         <v>1.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45981.75</v>
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="N26" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
-        <v>3.05</v>
+        <v>3.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="T26" t="n">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V26" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AF26" t="n">
         <v>1.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AH26" t="n">
         <v>1.53</v>
@@ -3634,67 +3634,67 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N27" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="P27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V27" t="n">
-        <v>8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG27" t="n">
         <v>1.3</v>

--- a/jogos_2025-11-20.xlsx
+++ b/jogos_2025-11-20.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,25 +871,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>6.56</v>
+        <v>4.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>5.99</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>6.55</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.86</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.79</v>
+        <v>2.46</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45981.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>6.56</v>
       </c>
       <c r="O5" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.99</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>6.55</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>3.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.46</v>
+        <v>1.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.48</v>
+        <v>2.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45981.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,23 +1109,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3.19</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>5.9</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
         <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AB6" t="n">
         <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,22 +1228,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>5.9</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AB7" t="n">
         <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45981.41666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2656,25 +2656,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby Talang</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>2.54</v>
       </c>
       <c r="M19" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.08</v>
+        <v>2.54</v>
       </c>
       <c r="O19" t="n">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
         <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45981.625</v>
@@ -2765,35 +2765,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N20" t="n">
-        <v>5.5</v>
+        <v>3.08</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V20" t="n">
         <v>5.25</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="W20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.17</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V20" t="n">
-        <v>9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC20" t="n">
-        <v>5.1</v>
+        <v>2.49</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45981.625</v>
@@ -3003,32 +3003,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.54</v>
+        <v>1.63</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.54</v>
+        <v>5.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.86</v>
+        <v>5.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="T22" t="n">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="U22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.44</v>
       </c>
-      <c r="V22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AC22" t="n">
-        <v>2.75</v>
+        <v>5.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45981.625</v>
@@ -3260,20 +3260,20 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3379,20 +3379,20 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
